--- a/Baker5/Few1.xlsx
+++ b/Baker5/Few1.xlsx
@@ -7127,22 +7127,22 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
@@ -7157,17 +7157,17 @@
       </c>
       <c r="O3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" s="10" t="inlineStr">
@@ -7205,7 +7205,7 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -7557,7 +7557,7 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -8002,17 +8002,17 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" s="10" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" s="10" t="inlineStr">
@@ -8359,17 +8359,17 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -8389,17 +8389,17 @@
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" s="10" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8535,22 +8535,22 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
@@ -8565,17 +8565,17 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" s="10" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8706,22 +8706,22 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R21" s="10" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -9053,7 +9053,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10031,12 +10031,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="P36" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" s="10" t="inlineStr">
@@ -10109,7 +10109,7 @@
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
@@ -10373,7 +10373,7 @@
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -10466,17 +10466,17 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -10501,17 +10501,17 @@
       </c>
       <c r="O41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R41" s="10" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="N42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" s="10" t="inlineStr">
@@ -10594,12 +10594,12 @@
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R42" s="10" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr">
@@ -10667,12 +10667,12 @@
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N43" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
@@ -10818,17 +10818,17 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
@@ -10843,12 +10843,12 @@
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O45" s="10" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="Q45" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R45" s="10" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -10994,17 +10994,17 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11082,17 +11082,17 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q48" s="10" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M49" s="9" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q49" s="10" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="P50" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q50" s="10" t="inlineStr">
@@ -11341,7 +11341,7 @@
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="O51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q51" s="10" t="inlineStr">
@@ -11429,7 +11429,7 @@
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -11517,7 +11517,7 @@
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -11527,17 +11527,17 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="O53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q53" s="10" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M54" s="9" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="P54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q54" s="10" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -11733,17 +11733,17 @@
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R55" s="10" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="P56" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q56" s="10" t="inlineStr">
@@ -11869,7 +11869,7 @@
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="P58" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q58" s="10" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -12163,27 +12163,27 @@
       </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N60" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R60" s="10" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -12236,12 +12236,12 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="P62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R62" s="10" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -12417,7 +12417,7 @@
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr">
@@ -12490,17 +12490,17 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="M64" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q65" s="10" t="inlineStr">
@@ -12671,12 +12671,12 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M66" s="9" t="inlineStr">
@@ -12696,22 +12696,22 @@
       </c>
       <c r="N66" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R66" s="10" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12759,12 +12759,12 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M67" s="9" t="inlineStr">
@@ -12784,22 +12784,22 @@
       </c>
       <c r="N67" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R67" s="10" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="S67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" s="9" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="S68" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="P70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q70" s="10" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="S70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13111,12 +13111,12 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K71" s="9" t="inlineStr">
@@ -13126,17 +13126,17 @@
       </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O71" s="10" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="P71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q71" s="10" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13199,12 +13199,12 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M72" s="9" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="N72" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O72" s="10" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="S72" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="P73" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q73" s="10" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="P74" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q74" s="10" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
@@ -13473,12 +13473,12 @@
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="L76" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="P76" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q76" s="10" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13634,17 +13634,17 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr">
@@ -13669,17 +13669,17 @@
       </c>
       <c r="O77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R77" s="10" t="inlineStr">
@@ -13722,12 +13722,12 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="N78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="P78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R78" s="10" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R79" s="10" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="P80" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q80" s="10" t="inlineStr">
@@ -13986,17 +13986,17 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K81" s="9" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="P81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S81" s="10" t="inlineStr">
@@ -14069,7 +14069,7 @@
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M82" s="9" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="P82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R82" s="10" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
@@ -14197,17 +14197,17 @@
       </c>
       <c r="O83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R83" s="10" t="inlineStr">
@@ -14250,17 +14250,17 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr">
@@ -14290,17 +14290,17 @@
       </c>
       <c r="P84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S84" s="10" t="inlineStr">
@@ -14338,17 +14338,17 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="N85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O85" s="10" t="inlineStr">
@@ -14378,17 +14378,17 @@
       </c>
       <c r="P85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S85" s="10" t="inlineStr">
@@ -14602,17 +14602,17 @@
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M88" s="9" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="R88" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S88" s="10" t="inlineStr">
@@ -14690,12 +14690,12 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="L89" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M89" s="9" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q89" s="10" t="inlineStr">
@@ -14740,12 +14740,12 @@
       </c>
       <c r="R89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L90" s="9" t="inlineStr">
